--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -53,15 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-04</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>2026-05-13</t>
   </si>
   <si>
     <t>В0584ВТ</t>
@@ -122,8 +113,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -209,11 +201,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -221,9 +214,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -577,20 +570,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>13</v>
+      <c r="A2" s="2">
+        <v>46146</v>
       </c>
       <c r="B2">
         <v>1147</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>27.614</v>
@@ -608,7 +601,7 @@
         <v>22.92</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -618,20 +611,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>14</v>
+      <c r="A3" s="2">
+        <v>46147</v>
       </c>
       <c r="B3">
         <v>1147</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>18.651</v>
@@ -649,7 +642,7 @@
         <v>28.35</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -659,20 +652,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>15</v>
+      <c r="A4" s="2">
+        <v>46155</v>
       </c>
       <c r="B4">
         <v>1147</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>19.591</v>
@@ -690,7 +683,7 @@
         <v>30.17</v>
       </c>
       <c r="K4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L4">
         <v>0</v>
@@ -699,115 +692,110 @@
         <v>180644</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="F5">
-        <v>65.85599999999999</v>
-      </c>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>32</v>
+      <c r="A9" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="6">
+        <v>38.242</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.5002</v>
+      </c>
+      <c r="E9" s="6">
+        <v>57.37</v>
+      </c>
+      <c r="F9" s="6">
+        <v>58.52</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1.15</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="5">
-        <v>38.242</v>
-      </c>
-      <c r="C10" s="5">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1.5002</v>
-      </c>
-      <c r="E10" s="5">
-        <v>57.37</v>
-      </c>
-      <c r="F10" s="5">
-        <v>58.52</v>
-      </c>
-      <c r="G10" s="5">
-        <v>1.15</v>
+      <c r="A10" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="6">
+        <v>27.614</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.8199</v>
+      </c>
+      <c r="E10" s="6">
+        <v>22.64</v>
+      </c>
+      <c r="F10" s="6">
+        <v>22.92</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.28</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="5">
-        <v>27.614</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0.8199</v>
-      </c>
-      <c r="E11" s="5">
-        <v>22.64</v>
-      </c>
-      <c r="F11" s="5">
-        <v>22.92</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="A11" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="8">
         <v>65.85599999999999</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C11" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8">
         <v>80.01000000000001</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F11" s="8">
         <v>81.44</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G11" s="8">
         <v>1.43</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -131,7 +131,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,12 +141,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -197,17 +191,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,34 +46,28 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
+  </si>
+  <si>
+    <t>ТубаТоп1</t>
   </si>
   <si>
     <t>В0584ВТ</t>
   </si>
   <si>
+    <t>78970155027720865</t>
+  </si>
+  <si>
     <t>78970155027720857</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:40:00</t>
-  </si>
-  <si>
-    <t>3232423264 3232423264</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -496,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +496,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -549,131 +537,203 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
+        <v>19.3</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="H2">
+        <v>29.72</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="J2">
+        <v>30.3</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>24.75</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="H3">
+        <v>17.32</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="J3">
+        <v>17.57</v>
+      </c>
+      <c r="K3">
+        <v>81293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F4">
+        <v>18.05</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H4">
+        <v>27.62</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J4">
+        <v>28.16</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="7">
+        <v>37.35</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.5352</v>
+      </c>
+      <c r="E9" s="7">
+        <v>57.34</v>
+      </c>
+      <c r="F9" s="7">
+        <v>58.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F2">
-        <v>31.11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2">
-        <v>0.77</v>
-      </c>
-      <c r="I2" s="1">
-        <v>23.95</v>
-      </c>
-      <c r="J2">
-        <v>0.78</v>
-      </c>
-      <c r="K2" s="1">
-        <v>24.27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>81049</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B10" s="7">
+        <v>24.75</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.6998</v>
+      </c>
+      <c r="E10" s="7">
+        <v>17.32</v>
+      </c>
+      <c r="F10" s="7">
+        <v>17.57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="7">
-        <v>31.11</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.7698</v>
-      </c>
-      <c r="E7" s="7">
-        <v>23.95</v>
-      </c>
-      <c r="F7" s="7">
-        <v>24.27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="10">
-        <v>31.11</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>23.95</v>
-      </c>
-      <c r="F8" s="10">
-        <v>24.27</v>
+      <c r="B11" s="10">
+        <v>62.1</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>74.66</v>
+      </c>
+      <c r="F11" s="10">
+        <v>76.03</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
@@ -68,6 +74,15 @@
   </si>
   <si>
     <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>14:59</t>
+  </si>
+  <si>
+    <t>15:10</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -487,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,10 +515,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -537,22 +554,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46174</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>19.3</v>
@@ -569,25 +592,31 @@
       <c r="J2">
         <v>30.3</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>190806</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46183</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>24.75</v>
@@ -604,25 +633,31 @@
       <c r="J3">
         <v>17.57</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
         <v>81293</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>196884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46188</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4">
         <v>18.05</v>
@@ -639,13 +674,19 @@
       <c r="J4">
         <v>28.16</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M4">
+        <v>199667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -653,18 +694,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -673,9 +714,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B9" s="7">
         <v>37.35</v>
@@ -693,9 +734,9 @@
         <v>58.46</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7">
         <v>24.75</v>
@@ -713,9 +754,9 @@
         <v>17.57</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B11" s="10">
         <v>62.1</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -49,40 +49,19 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Варненчик</t>
   </si>
   <si>
-    <t>ТубаТоп1</t>
-  </si>
-  <si>
     <t>В0584ВТ</t>
   </si>
   <si>
-    <t>78970155027720865</t>
-  </si>
-  <si>
     <t>78970155027720857</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>14:59</t>
-  </si>
-  <si>
-    <t>15:10</t>
+    <t>2026-06-19 12:23:27</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -502,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -515,12 +494,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,227 +531,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>18.7</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>12.16</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>12.34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46174</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
-        <v>19.3</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="H2">
-        <v>29.72</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="J2">
-        <v>30.3</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>190806</v>
+      <c r="B7" s="7">
+        <v>18.7</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.6503</v>
+      </c>
+      <c r="E7" s="7">
+        <v>12.16</v>
+      </c>
+      <c r="F7" s="7">
+        <v>12.34</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>24.75</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="H3">
-        <v>17.32</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="J3">
-        <v>17.57</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>81293</v>
-      </c>
-      <c r="M3">
-        <v>196884</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46188</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>18.05</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H4">
-        <v>27.62</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J4">
-        <v>28.16</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>199667</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>37.35</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.5352</v>
-      </c>
-      <c r="E9" s="7">
-        <v>57.34</v>
-      </c>
-      <c r="F9" s="7">
-        <v>58.46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>24.75</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B8" s="10">
+        <v>18.7</v>
+      </c>
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D10" s="8">
-        <v>0.6998</v>
-      </c>
-      <c r="E10" s="7">
-        <v>17.32</v>
-      </c>
-      <c r="F10" s="7">
-        <v>17.57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="10">
-        <v>62.1</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>74.66</v>
-      </c>
-      <c r="F11" s="10">
-        <v>76.03</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>12.16</v>
+      </c>
+      <c r="F8" s="10">
+        <v>12.34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В0584ВТ</t>
@@ -61,7 +70,13 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-19 12:23:27</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:23:00</t>
+  </si>
+  <si>
+    <t>3233575852 3233575852</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -481,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -490,14 +505,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,45 +549,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>18.7</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
         <v>0.65</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>12.16</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.66</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>12.34</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>81432</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -577,29 +613,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="7">
         <v>18.7</v>
@@ -617,9 +653,9 @@
         <v>12.34</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="10">
         <v>18.7</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>В0584ВТ</t>
@@ -70,13 +67,7 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:23:00</t>
-  </si>
-  <si>
-    <t>3233575852 3233575852</t>
+    <t>12:23</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -496,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,57 +545,51 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>18.7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H2">
+        <v>12.16</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J2">
+        <v>12.34</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>81432</v>
+      </c>
+      <c r="M2">
+        <v>116711</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="H2">
-        <v>0.65</v>
-      </c>
-      <c r="I2" s="1">
-        <v>12.16</v>
-      </c>
-      <c r="J2">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>12.34</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>81432</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -613,29 +597,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>18.7</v>
@@ -653,9 +637,9 @@
         <v>12.34</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>18.7</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,7 +55,10 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>ТубаТоп1</t>
@@ -73,13 +79,25 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-07-01 09:49:25</t>
-  </si>
-  <si>
-    <t>2026-07-02 12:06:40</t>
-  </si>
-  <si>
-    <t>2026-07-13 15:20:00</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:32:00</t>
+  </si>
+  <si>
+    <t>10:59:00</t>
+  </si>
+  <si>
+    <t>12:35:00</t>
+  </si>
+  <si>
+    <t>3235089712 3235089712</t>
+  </si>
+  <si>
+    <t>3235165162 3235165162</t>
+  </si>
+  <si>
+    <t>3235460835 3235460835</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -499,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,15 +526,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -553,124 +573,148 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46223</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>19.72</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.47</v>
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
       </c>
       <c r="H2">
-        <v>28.99</v>
+        <v>1.5</v>
       </c>
       <c r="I2" s="1">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="J2">
-        <v>29.58</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2">
+        <v>1.53</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46205</v>
+        <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>14.62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>0.63</v>
+      </c>
+      <c r="I3" s="1">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
+        <v>82011</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="F3">
-        <v>25.68</v>
-      </c>
-      <c r="G3" s="1">
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4">
+        <v>0.63</v>
+      </c>
+      <c r="I4" s="1">
+        <v>5.12</v>
+      </c>
+      <c r="J4">
         <v>0.64</v>
       </c>
-      <c r="H3">
-        <v>16.44</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="J3">
-        <v>16.69</v>
-      </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>81639</v>
+      <c r="K4" s="1">
+        <v>5.2</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
+        <v>82083</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46216</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
-        <v>29.1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H4">
-        <v>18.04</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J4">
-        <v>18.33</v>
-      </c>
-      <c r="K4" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4">
-        <v>81883</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -678,82 +722,82 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
-        <v>54.78</v>
+        <v>22.74</v>
       </c>
       <c r="C9" s="7">
         <v>2</v>
       </c>
       <c r="D9" s="8">
-        <v>0.6294</v>
+        <v>0.6302</v>
       </c>
       <c r="E9" s="7">
-        <v>34.48</v>
+        <v>14.33</v>
       </c>
       <c r="F9" s="7">
-        <v>35.02</v>
+        <v>14.56</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7">
-        <v>19.72</v>
+        <v>20</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
       </c>
       <c r="D10" s="8">
-        <v>1.4701</v>
+        <v>1.5</v>
       </c>
       <c r="E10" s="7">
-        <v>28.99</v>
+        <v>30</v>
       </c>
       <c r="F10" s="7">
-        <v>29.58</v>
+        <v>30.6</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B11" s="10">
-        <v>74.5</v>
+        <v>42.74</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>63.47</v>
+        <v>44.33</v>
       </c>
       <c r="F11" s="10">
-        <v>64.59999999999999</v>
+        <v>45.16</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -125,7 +125,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -753,7 +753,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="8">
-        <v>0.6302</v>
+        <v>0.630167</v>
       </c>
       <c r="E9" s="7">
         <v>14.33</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -517,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -530,13 +533,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,142 +582,154 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46223</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H2">
+        <v>1.389</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.5</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>30</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.53</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>30.6</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>25</v>
+      <c r="O2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3">
-        <v>14.62</v>
+        <v>14.625</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>9.210000000000001</v>
-      </c>
       <c r="J3">
+        <v>9.213749999999999</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>9.359999999999999</v>
       </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3">
         <v>82011</v>
       </c>
-      <c r="N3" t="s">
-        <v>26</v>
+      <c r="O3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>8.119999999999999</v>
+        <v>8.125</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1">
         <v>0.63</v>
       </c>
-      <c r="I4" s="1">
-        <v>5.12</v>
-      </c>
       <c r="J4">
+        <v>5.11875</v>
+      </c>
+      <c r="K4" s="1">
         <v>0.64</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>5.2</v>
       </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N4">
         <v>82083</v>
       </c>
-      <c r="N4" t="s">
-        <v>27</v>
+      <c r="O4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -722,38 +737,38 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="7">
-        <v>22.74</v>
+        <v>22.75</v>
       </c>
       <c r="C9" s="7">
         <v>2</v>
       </c>
       <c r="D9" s="8">
-        <v>0.630167</v>
+        <v>0.63</v>
       </c>
       <c r="E9" s="7">
         <v>14.33</v>
@@ -762,9 +777,9 @@
         <v>14.56</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7">
         <v>20</v>
@@ -782,12 +797,12 @@
         <v>30.6</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="10">
-        <v>42.74</v>
+        <v>42.75</v>
       </c>
       <c r="C11" s="10">
         <v>3</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -126,9 +123,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -222,10 +219,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,13 +530,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,154 +579,142 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46223</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
       <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2">
+        <v>1.5</v>
+      </c>
+      <c r="I2" s="1">
+        <v>30</v>
+      </c>
+      <c r="J2">
+        <v>1.53</v>
+      </c>
+      <c r="K2" s="1">
+        <v>30.6</v>
+      </c>
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="H2">
-        <v>1.389</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J2">
-        <v>30</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L2" s="1">
-        <v>30.6</v>
-      </c>
-      <c r="M2" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>26</v>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>14.625</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>9.214</v>
       </c>
       <c r="J3">
-        <v>9.213749999999999</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
         <v>9.359999999999999</v>
       </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3">
         <v>82011</v>
       </c>
-      <c r="O3" t="s">
-        <v>27</v>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>8.125</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I4" s="1">
-        <v>0.63</v>
+        <v>5.119</v>
       </c>
       <c r="J4">
-        <v>5.11875</v>
+        <v>0.64</v>
       </c>
       <c r="K4" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L4" s="1">
         <v>5.2</v>
       </c>
-      <c r="M4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4">
         <v>82083</v>
       </c>
-      <c r="O4" t="s">
+      <c r="N4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
         <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -737,69 +722,69 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
       <c r="E8" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" s="7">
         <v>22.75</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <v>2</v>
       </c>
       <c r="D9" s="8">
         <v>0.63</v>
       </c>
-      <c r="E9" s="7">
-        <v>14.33</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="E9" s="8">
+        <v>14.333</v>
+      </c>
+      <c r="F9" s="8">
         <v>14.56</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7">
         <v>20</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>1</v>
       </c>
       <c r="D10" s="8">
         <v>1.5</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <v>30</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>30.6</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="10">
         <v>42.75</v>
@@ -809,7 +794,7 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>44.33</v>
+        <v>44.333</v>
       </c>
       <c r="F11" s="10">
         <v>45.16</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1147 Варна Ситроен</t>
+    <t>Варна Варненчик</t>
   </si>
   <si>
     <t>ТубаТоп1</t>
@@ -79,25 +76,10 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:32:00</t>
-  </si>
-  <si>
-    <t>10:59:00</t>
-  </si>
-  <si>
-    <t>12:35:00</t>
-  </si>
-  <si>
-    <t>3235089712 3235089712</t>
-  </si>
-  <si>
-    <t>3235165162 3235165162</t>
-  </si>
-  <si>
-    <t>3235460835 3235460835</t>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>11:04</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -123,9 +105,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -219,10 +201,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -526,17 +508,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,233 +557,180 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46223</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>30.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>137243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>24.394</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3">
+        <v>15.856</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3">
+        <v>16.1</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.5</v>
-      </c>
-      <c r="I2" s="1">
-        <v>30</v>
-      </c>
-      <c r="J2">
-        <v>1.53</v>
-      </c>
-      <c r="K2" s="1">
-        <v>30.6</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L3">
+        <v>82285</v>
+      </c>
+      <c r="M3">
+        <v>236929</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="D7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46225</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="8" spans="1:13">
+      <c r="A8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="7">
+        <v>24.394</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E8" s="7">
+        <v>15.86</v>
+      </c>
+      <c r="F8" s="7">
+        <v>16.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B9" s="7">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>14.625</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>0.63</v>
-      </c>
-      <c r="I3" s="1">
-        <v>9.214</v>
-      </c>
-      <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>82011</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E9" s="7">
+        <v>30.4</v>
+      </c>
+      <c r="F9" s="7">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>8.125</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>0.63</v>
-      </c>
-      <c r="I4" s="1">
-        <v>5.119</v>
-      </c>
-      <c r="J4">
-        <v>0.64</v>
-      </c>
-      <c r="K4" s="1">
-        <v>5.2</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4">
-        <v>82083</v>
-      </c>
-      <c r="N4" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7">
-        <v>22.75</v>
-      </c>
-      <c r="C9" s="8">
+      <c r="B10" s="10">
+        <v>44.394</v>
+      </c>
+      <c r="C10" s="10">
         <v>2</v>
       </c>
-      <c r="D9" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E9" s="8">
-        <v>14.333</v>
-      </c>
-      <c r="F9" s="8">
-        <v>14.56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>20</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>30</v>
-      </c>
-      <c r="F10" s="8">
-        <v>30.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="10">
-        <v>42.75</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>44.333</v>
-      </c>
-      <c r="F11" s="10">
-        <v>45.16</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>46.26</v>
+      </c>
+      <c r="F10" s="10">
+        <v>47.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,31 +58,37 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>В0584ВТ</t>
   </si>
   <si>
     <t>ТубаТоп1</t>
   </si>
   <si>
-    <t>В0584ВТ</t>
+    <t>78970155027720857</t>
   </si>
   <si>
     <t>78970155027720865</t>
   </si>
   <si>
-    <t>78970155027720857</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>10:26</t>
-  </si>
-  <si>
-    <t>11:04</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:46:00</t>
+  </si>
+  <si>
+    <t>14:40:00</t>
+  </si>
+  <si>
+    <t>3236558842 3236558842</t>
+  </si>
+  <si>
+    <t>3236909762 3236909762</t>
   </si>
   <si>
     <t>Общи литри по продукт / КМЕТСТВО ТОПОЛИ</t>
@@ -104,10 +113,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -187,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -201,10 +211,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -499,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -508,16 +520,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,92 +570,101 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>14.29</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>82313</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46259</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>18</v>
-      </c>
-      <c r="F2">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>30.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J2">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>137243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46248</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
       </c>
       <c r="F3">
-        <v>24.394</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3">
-        <v>15.856</v>
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.459</v>
       </c>
       <c r="I3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J3">
-        <v>16.1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>82285</v>
+        <v>29.18</v>
+      </c>
+      <c r="J3" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K3" s="1">
+        <v>31.6</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
       </c>
       <c r="M3">
-        <v>236929</v>
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -650,82 +672,62 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7">
-        <v>24.394</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>0.65</v>
+        <v>30</v>
+      </c>
+      <c r="C8" s="8">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1.449</v>
       </c>
       <c r="E8" s="7">
-        <v>15.86</v>
+        <v>43.47</v>
       </c>
       <c r="F8" s="7">
-        <v>16.1</v>
+        <v>47.2</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="7">
-        <v>20</v>
-      </c>
-      <c r="C9" s="7">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E9" s="7">
-        <v>30.4</v>
-      </c>
-      <c r="F9" s="7">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="10">
-        <v>44.394</v>
-      </c>
-      <c r="C10" s="10">
+    <row r="9" spans="1:14">
+      <c r="A9" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="11">
+        <v>30</v>
+      </c>
+      <c r="C9" s="12">
         <v>2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>46.26</v>
-      </c>
-      <c r="F10" s="10">
-        <v>47.1</v>
+      <c r="D9" s="9"/>
+      <c r="E9" s="11">
+        <v>43.47</v>
+      </c>
+      <c r="F9" s="11">
+        <v>47.2</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КМЕТСТВО ТОПОЛИ/КМЕТСТВО ТОПОЛИ.xlsx
@@ -597,10 +597,10 @@
         <v>20</v>
       </c>
       <c r="H2" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I2" s="1">
-        <v>14.29</v>
+        <v>15.3</v>
       </c>
       <c r="J2" s="1">
         <v>1.56</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="H3" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I3" s="1">
-        <v>29.18</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1">
         <v>1.58</v>
@@ -703,10 +703,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="9">
-        <v>1.449</v>
+        <v>1.54333</v>
       </c>
       <c r="E8" s="7">
-        <v>43.47</v>
+        <v>46.3</v>
       </c>
       <c r="F8" s="7">
         <v>47.2</v>
@@ -724,7 +724,7 @@
       </c>
       <c r="D9" s="9"/>
       <c r="E9" s="11">
-        <v>43.47</v>
+        <v>46.3</v>
       </c>
       <c r="F9" s="11">
         <v>47.2</v>
